--- a/data/onboardmeasurements/Hsin_Tings_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
+++ b/data/onboardmeasurements/Hsin_Tings_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="390" uniqueCount="37">
   <si>
     <t>Board</t>
   </si>

--- a/data/onboardmeasurements/Hsin_Tings_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
+++ b/data/onboardmeasurements/Hsin_Tings_Board/Analysis/ImpliedField/Correlation_Summary.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" lastEdited="4" lowestEdited="4" rupBuild="4.6.0"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="261" uniqueCount="38">
   <si>
     <t>Board</t>
   </si>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -151,7 +151,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -159,12 +159,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -175,7 +177,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -290,7 +292,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -311,9 +313,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="true"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -334,7 +336,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -363,7 +365,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -372,7 +374,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -381,7 +383,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -404,7 +406,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -430,7 +432,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -458,1097 +460,1106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" customWidth="true"/>
+    <col min="2" max="2" width="15" customWidth="true"/>
+    <col min="3" max="3" width="8.5703125" customWidth="true"/>
+    <col min="4" max="4" width="22.85546875" customWidth="true"/>
+    <col min="5" max="5" width="15" customWidth="true"/>
+    <col min="6" max="6" width="14.85546875" customWidth="true"/>
+    <col min="7" max="7" width="19.7109375" customWidth="true"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D2">
-        <v>70.4211071202345</v>
-      </c>
-      <c r="E2">
-        <v>0.574827656868403</v>
-      </c>
-      <c r="F2">
-        <v>0.99046</v>
-      </c>
-      <c r="G2">
-        <v>-0.3389994079296413</v>
+      <c r="D2" s="0">
+        <v>70.421107120234495</v>
+      </c>
+      <c r="E2" s="0">
+        <v>0.25958126402057574</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.99046000000000001</v>
+      </c>
+      <c r="G2" s="0">
+        <v>-0.33899940792964056</v>
       </c>
       <c r="H2">
         <v>0.03031314067124717</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D3">
-        <v>89.1954143205806</v>
-      </c>
-      <c r="E3">
-        <v>0.3327525324712211</v>
-      </c>
-      <c r="F3">
-        <v>0.49963</v>
-      </c>
-      <c r="G3">
-        <v>-0.2261115442521726</v>
+      <c r="D3" s="0">
+        <v>89.195414320580596</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0.18700512943460074</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G3" s="0">
+        <v>-0.22611154425217259</v>
       </c>
       <c r="H3">
         <v>0.03187252318965995</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D4">
-        <v>81.6326006128586</v>
-      </c>
-      <c r="E4">
-        <v>0.398615256107316</v>
-      </c>
-      <c r="F4">
-        <v>0.49963</v>
-      </c>
-      <c r="G4">
-        <v>-0.3326446899519259</v>
+      <c r="D4" s="0">
+        <v>81.632600612858596</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0.19979762836844567</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G4" s="0">
+        <v>-0.33264468995192575</v>
       </c>
       <c r="H4">
         <v>0.02016546303775192</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
-        <v>103.142052337632</v>
-      </c>
-      <c r="E5">
-        <v>0.3489362406924571</v>
-      </c>
-      <c r="F5">
-        <v>0.49963</v>
-      </c>
-      <c r="G5">
-        <v>-0.3138565272473866</v>
+      <c r="D5" s="0">
+        <v>103.14205233763199</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0.19662203282142329</v>
+      </c>
+      <c r="F5" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G5" s="0">
+        <v>-0.31385652724738655</v>
       </c>
       <c r="H5">
         <v>0.02744895470481432</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+    <row r="6">
+      <c r="A6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6">
-        <v>70.4211071202345</v>
-      </c>
-      <c r="E6">
-        <v>0.9257167725111057</v>
-      </c>
-      <c r="F6">
-        <v>0.49963</v>
-      </c>
-      <c r="G6">
-        <v>0.9228220549533516</v>
+      <c r="D6" s="0">
+        <v>70.421107120234495</v>
+      </c>
+      <c r="E6" s="0">
+        <v>0.43921490679195813</v>
+      </c>
+      <c r="F6" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.92282205495335146</v>
       </c>
       <c r="H6">
         <v>0.01672920268631911</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
+    <row r="7">
+      <c r="A7" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7">
-        <v>89.1954143205806</v>
-      </c>
-      <c r="E7">
-        <v>1.098262738574482</v>
-      </c>
-      <c r="F7">
-        <v>0.49963</v>
-      </c>
-      <c r="G7">
-        <v>1.058282169382927</v>
+      <c r="D7" s="0">
+        <v>89.195414320580596</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0.53455662898362788</v>
+      </c>
+      <c r="F7" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1.0582821693829272</v>
       </c>
       <c r="H7">
         <v>0.02130322367147729</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+    <row r="8">
+      <c r="A8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8">
-        <v>81.6326006128586</v>
-      </c>
-      <c r="E8">
-        <v>1.13704573054333</v>
-      </c>
-      <c r="F8">
-        <v>0.49963</v>
-      </c>
-      <c r="G8">
-        <v>1.110912094681865</v>
+      <c r="D8" s="0">
+        <v>81.632600612858596</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.57121786700315314</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1.1109120946818645</v>
       </c>
       <c r="H8">
         <v>0.0175477204960578</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+    <row r="9">
+      <c r="A9" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D9">
-        <v>70.4211071202345</v>
-      </c>
-      <c r="E9">
-        <v>1.006658413917923</v>
-      </c>
-      <c r="F9">
-        <v>0.49963</v>
-      </c>
-      <c r="G9">
-        <v>-0.9377803825081402</v>
+      <c r="D9" s="0">
+        <v>70.421107120234495</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0.51660647620724653</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G9" s="0">
+        <v>-0.93778038250814022</v>
       </c>
       <c r="H9">
         <v>0.01779795436854223</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+    <row r="10">
+      <c r="A10" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D10">
-        <v>89.1954143205806</v>
-      </c>
-      <c r="E10">
-        <v>1.088284647135827</v>
-      </c>
-      <c r="F10">
-        <v>0.49963</v>
-      </c>
-      <c r="G10">
+      <c r="D10" s="0">
+        <v>89.195414320580596</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0.54195611252228615</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G10" s="0">
         <v>-1.042738915201884</v>
       </c>
       <c r="H10">
         <v>0.02320445961703889</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
+    <row r="11">
+      <c r="A11" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D11">
-        <v>81.6326006128586</v>
-      </c>
-      <c r="E11">
-        <v>1.125898223381187</v>
-      </c>
-      <c r="F11">
-        <v>0.49963</v>
-      </c>
-      <c r="G11">
-        <v>-1.107979863737765</v>
+      <c r="D11" s="0">
+        <v>81.632600612858596</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0.57134036708188352</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G11" s="0">
+        <v>-1.1079798637377638</v>
       </c>
       <c r="H11">
         <v>0.01427838297494269</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
+    <row r="12">
+      <c r="A12" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D12">
-        <v>103.142052337632</v>
-      </c>
-      <c r="E12">
-        <v>1.155784641649065</v>
-      </c>
-      <c r="F12">
-        <v>0.49963</v>
-      </c>
-      <c r="G12">
-        <v>-1.100615137136783</v>
+      <c r="D12" s="0">
+        <v>103.14205233763199</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0.66965896484104681</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G12" s="0">
+        <v>-1.1006151371367832</v>
       </c>
       <c r="H12">
         <v>0.04217736505121661</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D13">
-        <v>76.6802914781064</v>
-      </c>
-      <c r="E13">
-        <v>0.9333558678561037</v>
-      </c>
-      <c r="F13">
-        <v>0.49963</v>
-      </c>
-      <c r="G13">
-        <v>0.8829957942664065</v>
+      <c r="D13" s="0">
+        <v>76.680291478106398</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0.44248658091884263</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.88299579426640662</v>
       </c>
       <c r="H13">
         <v>0.02903656924738609</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
+    <row r="14">
+      <c r="A14" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D14">
-        <v>88.2667363442592</v>
-      </c>
-      <c r="E14">
-        <v>1.090671344463564</v>
-      </c>
-      <c r="F14">
-        <v>0.49963</v>
-      </c>
-      <c r="G14">
+      <c r="D14" s="0">
+        <v>88.266736344259201</v>
+      </c>
+      <c r="E14" s="0">
+        <v>0.506079660924311</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G14" s="0">
         <v>1.028570172059353</v>
       </c>
       <c r="H14">
         <v>0.01991175259182035</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
+    <row r="15">
+      <c r="A15" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <v>101.093858541453</v>
       </c>
-      <c r="E15">
-        <v>1.146063684496648</v>
-      </c>
-      <c r="F15">
-        <v>0.49963</v>
-      </c>
-      <c r="G15">
-        <v>1.148155351723488</v>
+      <c r="E15" s="0">
+        <v>0.5778788231338845</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1.1481553517234888</v>
       </c>
       <c r="H15">
         <v>0.01182196521570634</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
+    <row r="16">
+      <c r="A16" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <v>105.816034350062</v>
       </c>
-      <c r="E16">
-        <v>1.134516150953568</v>
-      </c>
-      <c r="F16">
-        <v>0.49963</v>
-      </c>
-      <c r="G16">
-        <v>1.121686384458586</v>
+      <c r="E16" s="0">
+        <v>0.54424644009511625</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G16" s="0">
+        <v>1.1216863844585849</v>
       </c>
       <c r="H16">
         <v>0.01201374974364932</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
+    <row r="17">
+      <c r="A17" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D17">
-        <v>76.6802914781064</v>
-      </c>
-      <c r="E17">
-        <v>1.061028830638057</v>
-      </c>
-      <c r="F17">
-        <v>0.49963</v>
-      </c>
-      <c r="G17">
-        <v>-0.9634441256687458</v>
+      <c r="D17" s="0">
+        <v>76.680291478106398</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0.50730114935876813</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G17" s="0">
+        <v>-0.96344412566874571</v>
       </c>
       <c r="H17">
         <v>0.02556162917901492</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
+    <row r="18">
+      <c r="A18" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D18">
-        <v>88.2667363442592</v>
-      </c>
-      <c r="E18">
-        <v>1.202378204922802</v>
-      </c>
-      <c r="F18">
-        <v>0.49963</v>
-      </c>
-      <c r="G18">
-        <v>-1.139797684703567</v>
+      <c r="D18" s="0">
+        <v>88.266736344259201</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0.59286206975981892</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G18" s="0">
+        <v>-1.1397976847035671</v>
       </c>
       <c r="H18">
         <v>0.0522938888486191</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <v>101.093858541453</v>
       </c>
-      <c r="E19">
-        <v>1.261698799909734</v>
-      </c>
-      <c r="F19">
-        <v>0.49963</v>
-      </c>
-      <c r="G19">
-        <v>-1.217061409259668</v>
+      <c r="E19" s="0">
+        <v>0.64415386789587448</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G19" s="0">
+        <v>-1.2170614092596677</v>
       </c>
       <c r="H19">
         <v>0.02971154096059511</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
+    <row r="20">
+      <c r="A20" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <v>105.816034350062</v>
       </c>
-      <c r="E20">
-        <v>1.20388181982483</v>
-      </c>
-      <c r="F20">
-        <v>0.49963</v>
-      </c>
-      <c r="G20">
+      <c r="E20" s="0">
+        <v>0.62665361074324577</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G20" s="0">
         <v>-1.176568044832152</v>
       </c>
       <c r="H20">
         <v>0.01751245597409875</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
+    <row r="21">
+      <c r="A21" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D21">
-        <v>6.247517526941571</v>
-      </c>
-      <c r="E21">
-        <v>1.488591262031782</v>
-      </c>
-      <c r="F21">
-        <v>0.49963</v>
-      </c>
-      <c r="G21">
-        <v>1.161841368072911</v>
+      <c r="D21" s="0">
+        <v>6.2475175269415715</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0.74749690254721379</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G21" s="0">
+        <v>1.1618413680729127</v>
       </c>
       <c r="H21">
         <v>0.1220358052072823</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
+    <row r="22">
+      <c r="A22" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D22">
-        <v>6.428293863995808</v>
-      </c>
-      <c r="E22">
-        <v>1.38139297733934</v>
-      </c>
-      <c r="F22">
-        <v>0.49963</v>
-      </c>
-      <c r="G22">
-        <v>1.054269686799796</v>
+      <c r="D22" s="0">
+        <v>6.4282938639958083</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0.73580954761502571</v>
+      </c>
+      <c r="F22" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G22" s="0">
+        <v>1.0542696867997967</v>
       </c>
       <c r="H22">
         <v>0.1055306929754245</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
+    <row r="23">
+      <c r="A23" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D23">
-        <v>13.56638498476472</v>
-      </c>
-      <c r="E23">
-        <v>1.260468431288227</v>
-      </c>
-      <c r="F23">
-        <v>0.49963</v>
-      </c>
-      <c r="G23">
-        <v>1.209956780369983</v>
+      <c r="D23" s="0">
+        <v>13.566384984764722</v>
+      </c>
+      <c r="E23" s="0">
+        <v>0.6059093862685131</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G23" s="0">
+        <v>1.2099567803699831</v>
       </c>
       <c r="H23">
         <v>0.04181219278109095</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
+    <row r="24">
+      <c r="A24" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D24">
-        <v>17.17219779048767</v>
-      </c>
-      <c r="E24">
-        <v>1.181561046963964</v>
-      </c>
-      <c r="F24">
-        <v>0.49963</v>
-      </c>
-      <c r="G24">
-        <v>1.180500586553804</v>
+      <c r="D24" s="0">
+        <v>17.172197790487669</v>
+      </c>
+      <c r="E24" s="0">
+        <v>0.66036975222154959</v>
+      </c>
+      <c r="F24" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.1805005865538032</v>
       </c>
       <c r="H24">
         <v>0.04557609421879229</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
+    <row r="25">
+      <c r="A25" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D25">
-        <v>6.247517526941571</v>
-      </c>
-      <c r="E25">
-        <v>1.198876188453791</v>
-      </c>
-      <c r="F25">
-        <v>0.49963</v>
-      </c>
-      <c r="G25">
+      <c r="D25" s="0">
+        <v>6.2475175269415715</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.74749690254721379</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G25" s="0">
         <v>-1.038076279747324</v>
       </c>
       <c r="H25">
         <v>0.1011584019152773</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
+    <row r="26">
+      <c r="A26" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D26">
-        <v>6.428293863995808</v>
-      </c>
-      <c r="E26">
-        <v>1.61784763111885</v>
-      </c>
-      <c r="F26">
-        <v>0.49963</v>
-      </c>
-      <c r="G26">
-        <v>-1.197177732037477</v>
+      <c r="D26" s="0">
+        <v>6.4282938639958083</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.91937302883814554</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G26" s="0">
+        <v>-1.1971777320374772</v>
       </c>
       <c r="H26">
         <v>0.1081863130281259</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
+    <row r="27">
+      <c r="A27" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D27">
-        <v>13.56638498476472</v>
-      </c>
-      <c r="E27">
-        <v>1.222138397120094</v>
-      </c>
-      <c r="F27">
-        <v>0.49963</v>
-      </c>
-      <c r="G27">
-        <v>-1.165322304017615</v>
+      <c r="D27" s="0">
+        <v>13.566384984764722</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.58084744085080531</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G27" s="0">
+        <v>-1.1653223040176142</v>
       </c>
       <c r="H27">
         <v>0.04245572833960318</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
+    <row r="28">
+      <c r="A28" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D28">
-        <v>17.17219779048767</v>
-      </c>
-      <c r="E28">
-        <v>1.196119463018226</v>
-      </c>
-      <c r="F28">
-        <v>0.49963</v>
-      </c>
-      <c r="G28">
-        <v>-1.107885794743615</v>
+      <c r="D28" s="0">
+        <v>17.172197790487669</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.6749281682758117</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G28" s="0">
+        <v>-1.1078857947436152</v>
       </c>
       <c r="H28">
         <v>0.04731650155128923</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
+    <row r="29">
+      <c r="A29" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="D29">
-        <v>31.54263740199321</v>
-      </c>
-      <c r="E29">
-        <v>1.191403227354318</v>
-      </c>
-      <c r="F29">
-        <v>0.49963</v>
-      </c>
-      <c r="G29">
-        <v>1.126611638494348</v>
+      <c r="D29" s="0">
+        <v>31.542637401993211</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0.60616364308163817</v>
+      </c>
+      <c r="F29" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.1266116384943492</v>
       </c>
       <c r="H29">
         <v>0.03957200961395028</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
+    <row r="30">
+      <c r="A30" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D30">
-        <v>40.40807123866232</v>
-      </c>
-      <c r="E30">
-        <v>1.187139067259009</v>
-      </c>
-      <c r="F30">
-        <v>0.49963</v>
-      </c>
-      <c r="G30">
-        <v>1.093871535677425</v>
+      <c r="D30" s="0">
+        <v>40.408071238662316</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0.55681944993385557</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.093871535677424</v>
       </c>
       <c r="H30">
         <v>0.04447812133267133</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
+    <row r="31">
+      <c r="A31" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D31">
-        <v>62.18873193138286</v>
-      </c>
-      <c r="E31">
-        <v>1.264859365307441</v>
-      </c>
-      <c r="F31">
-        <v>0.49963</v>
-      </c>
-      <c r="G31">
-        <v>1.258371382450012</v>
+      <c r="D31" s="0">
+        <v>62.188731931382861</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0.63516329684263517</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.2583713824500129</v>
       </c>
       <c r="H31">
         <v>0.02299598366364076</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
+    <row r="32">
+      <c r="A32" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D32">
-        <v>66.7132570229962</v>
-      </c>
-      <c r="E32">
-        <v>1.175928196294707</v>
-      </c>
-      <c r="F32">
-        <v>0.49963</v>
-      </c>
-      <c r="G32">
-        <v>1.129358260999982</v>
+      <c r="D32" s="0">
+        <v>66.713257022996203</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0.61142270397521137</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.1293582609999811</v>
       </c>
       <c r="H32">
         <v>0.02658250744125834</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
+    <row r="33">
+      <c r="A33" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="D33">
-        <v>31.54263740199321</v>
-      </c>
-      <c r="E33">
-        <v>1.257979778111394</v>
-      </c>
-      <c r="F33">
-        <v>0.49963</v>
-      </c>
-      <c r="G33">
-        <v>-1.106671128015134</v>
+      <c r="D33" s="0">
+        <v>31.542637401993211</v>
+      </c>
+      <c r="E33" s="0">
+        <v>0.76499627131622983</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G33" s="0">
+        <v>-1.1066711280151342</v>
       </c>
       <c r="H33">
         <v>0.05244787285120969</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
+    <row r="34">
+      <c r="A34" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D34">
-        <v>40.40807123866232</v>
-      </c>
-      <c r="E34">
-        <v>1.247275567851692</v>
-      </c>
-      <c r="F34">
-        <v>0.49963</v>
-      </c>
-      <c r="G34">
-        <v>-1.187647225944931</v>
+      <c r="D34" s="0">
+        <v>40.408071238662316</v>
+      </c>
+      <c r="E34" s="0">
+        <v>0.59864277750672279</v>
+      </c>
+      <c r="F34" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G34" s="0">
+        <v>-1.187647225944932</v>
       </c>
       <c r="H34">
         <v>0.04636133988966736</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
+    <row r="35">
+      <c r="A35" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D35">
-        <v>62.18873193138286</v>
-      </c>
-      <c r="E35">
-        <v>1.431127428328976</v>
-      </c>
-      <c r="F35">
-        <v>0.49963</v>
-      </c>
-      <c r="G35">
-        <v>-1.257891045781097</v>
+      <c r="D35" s="0">
+        <v>62.188731931382861</v>
+      </c>
+      <c r="E35" s="0">
+        <v>0.80223536403743545</v>
+      </c>
+      <c r="F35" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G35" s="0">
+        <v>-1.2578910457810963</v>
       </c>
       <c r="H35">
         <v>0.03585222370635363</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
+    <row r="36">
+      <c r="A36" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D36">
-        <v>66.7132570229962</v>
-      </c>
-      <c r="E36">
-        <v>1.192716463724211</v>
-      </c>
-      <c r="F36">
-        <v>0.49963</v>
-      </c>
-      <c r="G36">
-        <v>-1.182579302192581</v>
+      <c r="D36" s="0">
+        <v>66.713257022996203</v>
+      </c>
+      <c r="E36" s="0">
+        <v>0.572749730789201</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G36" s="0">
+        <v>-1.1825793021925821</v>
       </c>
       <c r="H36">
         <v>0.0333426209514214</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
+    <row r="37">
+      <c r="A37" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D37">
-        <v>12.11419567114783</v>
-      </c>
-      <c r="E37">
-        <v>1.19529190324125</v>
-      </c>
-      <c r="F37">
-        <v>0.49963</v>
-      </c>
-      <c r="G37">
-        <v>1.067114782949853</v>
+      <c r="D37" s="0">
+        <v>12.114195671147829</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0.63891984330682283</v>
+      </c>
+      <c r="F37" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G37" s="0">
+        <v>1.0671147829498531</v>
       </c>
       <c r="H37">
         <v>0.05256937207297173</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
+    <row r="38">
+      <c r="A38" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D38">
-        <v>20.11704919548161</v>
-      </c>
-      <c r="E38">
-        <v>1.236761900725756</v>
-      </c>
-      <c r="F38">
-        <v>0.49963</v>
-      </c>
-      <c r="G38">
-        <v>1.16738980080529</v>
+      <c r="D38" s="0">
+        <v>20.117049195481606</v>
+      </c>
+      <c r="E38" s="0">
+        <v>0.56916896154774133</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G38" s="0">
+        <v>1.167389800805289</v>
       </c>
       <c r="H38">
         <v>0.03636911473848155</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
+    <row r="39">
+      <c r="A39" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D39">
-        <v>28.74885696895134</v>
-      </c>
-      <c r="E39">
-        <v>1.181960035374675</v>
-      </c>
-      <c r="F39">
-        <v>0.49963</v>
-      </c>
-      <c r="G39">
-        <v>1.112341313167999</v>
+      <c r="D39" s="0">
+        <v>28.748856968951344</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0.57254450212667118</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G39" s="0">
+        <v>1.1123413131679991</v>
       </c>
       <c r="H39">
         <v>0.07079178691577095</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
+    <row r="40">
+      <c r="A40" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D40">
-        <v>12.11419567114783</v>
-      </c>
-      <c r="E40">
-        <v>1.298476632457495</v>
-      </c>
-      <c r="F40">
-        <v>0.49963</v>
-      </c>
-      <c r="G40">
-        <v>-1.251565838131907</v>
+      <c r="D40" s="0">
+        <v>12.114195671147829</v>
+      </c>
+      <c r="E40" s="0">
+        <v>0.78337846420956625</v>
+      </c>
+      <c r="F40" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G40" s="0">
+        <v>-1.2515658381319079</v>
       </c>
       <c r="H40">
         <v>0.07034294831756582</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" t="s">
+    <row r="41">
+      <c r="A41" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D41">
-        <v>20.11704919548161</v>
-      </c>
-      <c r="E41">
-        <v>1.252668806201316</v>
-      </c>
-      <c r="F41">
-        <v>0.49963</v>
-      </c>
-      <c r="G41">
-        <v>-1.178839312275561</v>
+      <c r="D41" s="0">
+        <v>20.117049195481606</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0.68499111704185201</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G41" s="0">
+        <v>-1.1788393122755618</v>
       </c>
       <c r="H41">
         <v>0.04298326819306235</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" t="s">
+    <row r="42">
+      <c r="A42" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D42">
-        <v>28.74885696895134</v>
-      </c>
-      <c r="E42">
-        <v>1.158306921070524</v>
-      </c>
-      <c r="F42">
-        <v>0.49963</v>
-      </c>
-      <c r="G42">
-        <v>-1.087200731275997</v>
+      <c r="D42" s="0">
+        <v>28.748856968951344</v>
+      </c>
+      <c r="E42" s="0">
+        <v>0.59967601559339812</v>
+      </c>
+      <c r="F42" s="0">
+        <v>0.49963000000000002</v>
+      </c>
+      <c r="G42" s="0">
+        <v>-1.0872007312759984</v>
       </c>
       <c r="H42">
         <v>0.05040312898113641</v>
